--- a/data/raw/附件3 市主城区 10 区域分时段充电负荷.xlsx
+++ b/data/raw/附件3 市主城区 10 区域分时段充电负荷.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="工作日分时段充电负荷数据" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="26">
   <si>
     <t>区域</t>
   </si>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>充电负荷按延安市主流充电桩功率测算，快充桩单枪充电负荷按120kWh / 小时、慢充桩按 7kWh / 小时，混合负荷按实际车次比例折算。</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1081,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
@@ -2088,9 +2085,6 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
       <c r="W14" t="s">
         <v>25</v>
       </c>
@@ -2114,7 +2108,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
